--- a/TPDS/Nekbone.xlsx
+++ b/TPDS/Nekbone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimojima/Experimental-Data/TPDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F803B804-D0CD-5544-BB4C-F1E1F09213BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BCD9AA-E6B0-F74C-8DE9-2F60411A3CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{CDDF401D-2DE4-9646-B3FA-38F148DD2580}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" activeTab="1" xr2:uid="{CDDF401D-2DE4-9646-B3FA-38F148DD2580}"/>
   </bookViews>
   <sheets>
     <sheet name="nekbone_metrics_summary" sheetId="4" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
   <si>
     <t>file</t>
   </si>
@@ -163,6 +163,26 @@
   </si>
   <si>
     <t>Setup Flop</t>
+  </si>
+  <si>
+    <t>Native+UNENC</t>
+  </si>
+  <si>
+    <t>Native+ENC</t>
+  </si>
+  <si>
+    <t>TEE+UNENC</t>
+  </si>
+  <si>
+    <t>TEE+ENC</t>
+  </si>
+  <si>
+    <t>Native+UNENC (Baseline)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TEE+ENC (Proposal)</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -331,99 +351,13 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Native+UNENC</c:v>
+                  <c:v>Native+UNENC (Baseline)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>8</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Nekbone!$D$28:$D$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5878.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11848</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>24416</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>42316</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CDBB-7949-92DA-4996094974DC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Nekbone!$E$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Native+ENC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
@@ -436,7 +370,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
@@ -475,21 +409,105 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>Nekbone!$D$28:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.8784999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.848000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.416</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42.316000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CDBB-7949-92DA-4996094974DC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Nekbone!$E$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Native+ENC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="44450" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>Nekbone!$H$28:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5872</c:v>
+                  <c:v>5.8719999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11847</c:v>
+                  <c:v>11.847</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24174</c:v>
+                  <c:v>24.173999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41635</c:v>
+                  <c:v>41.634999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -516,7 +534,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="60000"/>
@@ -529,7 +547,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2">
@@ -573,16 +591,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4961.2</c:v>
+                  <c:v>4.9611999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9772.4</c:v>
+                  <c:v>9.7723999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20053</c:v>
+                  <c:v>20.053000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34974</c:v>
+                  <c:v>34.973999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,17 +621,15 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TEE+ENC</c:v>
+                  <c:v>TEE+ENC (Proposal)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -621,18 +637,14 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -663,16 +675,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4946.7</c:v>
+                  <c:v>4.9466999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9525.4</c:v>
+                  <c:v>9.5253999999999994</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18771</c:v>
+                  <c:v>18.771000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32372</c:v>
+                  <c:v>32.372</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -711,7 +723,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -725,7 +737,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Number of Processes</a:t>
+                  <a:t>Number of Nodes</a:t>
                 </a:r>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -744,7 +756,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -782,7 +794,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -832,7 +844,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -846,7 +858,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>MFlops</a:t>
+                  <a:t>GFlops</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -864,7 +876,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -896,7 +908,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -924,18 +936,18 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="r"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.13022185180984372"/>
-          <c:y val="2.7103879239682833E-2"/>
-          <c:w val="0.1881043415529618"/>
-          <c:h val="0.41359089235742608"/>
+          <c:x val="0.11535481675901621"/>
+          <c:y val="3.2394138232720908E-2"/>
+          <c:w val="0.25655876348789736"/>
+          <c:h val="0.22132283464566929"/>
         </c:manualLayout>
       </c:layout>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -948,7 +960,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -990,7 +1002,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2000"/>
+        <a:defRPr sz="2800" b="1"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -1563,16 +1575,759 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>640522</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>17355</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>643560</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>254571</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>102755</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>116388</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="グループ化 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CDA6618-1945-BC48-9890-70621D57D330}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10422064" y="4233333"/>
+          <a:ext cx="4840056" cy="2696706"/>
+          <a:chOff x="18846605" y="6604733"/>
+          <a:chExt cx="4706375" cy="2794741"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="5" name="グループ化 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3959C030-4D60-CF5D-7710-B50D9F15F4E7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18890767" y="6604733"/>
+            <a:ext cx="4662213" cy="507996"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="4699891" cy="508000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="テキスト ボックス 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CDD7952-1686-D2A2-9BF3-E5A1DD88B77E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="3958836" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>Native+Unenc (Baseline)</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="19" name="直線コネクタ 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24547D82-1821-BEC6-C899-EBB9B136D1C6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="円/楕円 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0977FF9-9668-C912-986F-98B9D921828A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26128440" y="4521055"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="6" name="グループ化 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8D8574-5DF1-B235-CA55-C0BDE5E7CACD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18895895" y="7345660"/>
+            <a:ext cx="2641875" cy="507997"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="2663992" cy="508000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="テキスト ボックス 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E04904D-6A6C-E9A7-5B5D-6D4CBED82B9A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="1922937" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>Native+Enc </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="16" name="直線コネクタ 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E83B086B-7FE8-DB2B-FF92-F9DDF4727223}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="円/楕円 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{350BD13B-D008-983E-361B-CC0FF7180D35}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26136899" y="4521056"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E1AF280-664C-2792-4CD4-8F0EFBF3410A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18898245" y="8133622"/>
+            <a:ext cx="2641875" cy="507995"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="2663992" cy="508000"/>
+          </a:xfrm>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="テキスト ボックス 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE04703F-2C02-A18B-60D6-808C4381F909}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="1922937" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>TEE+Unenc </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="13" name="直線コネクタ 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA53C5E3-AADF-7D82-05B3-E8A7861E6787}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="円/楕円 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{201AB40B-329B-644D-11BB-DCF37B5CB601}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26136899" y="4512588"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="8" name="グループ化 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF62B50-2F04-74E9-E711-1B51ED0585C4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18846605" y="8891478"/>
+            <a:ext cx="3808895" cy="507996"/>
+            <a:chOff x="25901800" y="4289778"/>
+            <a:chExt cx="3839421" cy="508000"/>
+          </a:xfrm>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="テキスト ボックス 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D720EFB1-066B-010F-4D89-1FBF8C217FAD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26670561" y="4289778"/>
+              <a:ext cx="3070660" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>TEE+Enc (Proposal) </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="10" name="直線コネクタ 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72E9A757-9D06-7978-6158-A6F5B00F2932}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25901800" y="4551948"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="円/楕円 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{992A8793-64D1-3CD2-919D-FA3A2C42A89D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26150751" y="4478723"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>141112</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>20160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>493486</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>254001</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2579,7 +3334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874C2D45-1706-F843-8755-C2FE695FD393}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3128,7 +3883,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>15</v>
@@ -3137,7 +3892,8 @@
         <v>1</v>
       </c>
       <c r="D28" s="3">
-        <v>5878.5</v>
+        <f>5878.5/1000</f>
+        <v>5.8784999999999998</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>28</v>
@@ -3149,7 +3905,8 @@
         <v>1</v>
       </c>
       <c r="H28" s="3">
-        <v>5872</v>
+        <f>5872/1000</f>
+        <v>5.8719999999999999</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>31</v>
@@ -3161,10 +3918,11 @@
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>4961.2</v>
+        <f>4961.2/1000</f>
+        <v>4.9611999999999998</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>10</v>
@@ -3173,7 +3931,8 @@
         <v>1</v>
       </c>
       <c r="P28" s="3">
-        <v>4946.7</v>
+        <f>4946.7/1000</f>
+        <v>4.9466999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3187,7 +3946,8 @@
         <v>2</v>
       </c>
       <c r="D29" s="5">
-        <v>11848</v>
+        <f>11848/1000</f>
+        <v>11.848000000000001</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>28</v>
@@ -3199,7 +3959,8 @@
         <v>2</v>
       </c>
       <c r="H29" s="5">
-        <v>11847</v>
+        <f>11847/1000</f>
+        <v>11.847</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>31</v>
@@ -3211,7 +3972,8 @@
         <v>2</v>
       </c>
       <c r="L29" s="5">
-        <v>9772.4</v>
+        <f>9772.4/1000</f>
+        <v>9.7723999999999993</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>30</v>
@@ -3223,7 +3985,8 @@
         <v>2</v>
       </c>
       <c r="P29" s="5">
-        <v>9525.4</v>
+        <f>9525.4/1000</f>
+        <v>9.5253999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3237,7 +4000,8 @@
         <v>4</v>
       </c>
       <c r="D30" s="3">
-        <v>24416</v>
+        <f>24416/1000</f>
+        <v>24.416</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>28</v>
@@ -3249,7 +4013,8 @@
         <v>4</v>
       </c>
       <c r="H30" s="3">
-        <v>24174</v>
+        <f>24174/1000</f>
+        <v>24.173999999999999</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>31</v>
@@ -3261,7 +4026,8 @@
         <v>4</v>
       </c>
       <c r="L30" s="3">
-        <v>20053</v>
+        <f>20053/1000</f>
+        <v>20.053000000000001</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>30</v>
@@ -3273,7 +4039,8 @@
         <v>4</v>
       </c>
       <c r="P30" s="3">
-        <v>18771</v>
+        <f>18771/1000</f>
+        <v>18.771000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3287,7 +4054,8 @@
         <v>8</v>
       </c>
       <c r="D31" s="5">
-        <v>42316</v>
+        <f>42316/1000</f>
+        <v>42.316000000000003</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>28</v>
@@ -3299,7 +4067,8 @@
         <v>8</v>
       </c>
       <c r="H31" s="5">
-        <v>41635</v>
+        <f>41635/1000</f>
+        <v>41.634999999999998</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>31</v>
@@ -3311,7 +4080,8 @@
         <v>8</v>
       </c>
       <c r="L31" s="5">
-        <v>34974</v>
+        <f>34974/1000</f>
+        <v>34.973999999999997</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>30</v>
@@ -3323,23 +4093,240 @@
         <v>8</v>
       </c>
       <c r="P31" s="5">
-        <v>32372</v>
+        <f>32372/1000</f>
+        <v>32.372</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="D32">
         <f>D31/D28</f>
-        <v>7.1984349749085652</v>
+        <v>7.1984349749085661</v>
       </c>
       <c r="H32">
         <f>H31/H28</f>
-        <v>7.0904291553133518</v>
+        <v>7.0904291553133509</v>
       </c>
       <c r="L32">
         <f>L31/L28</f>
-        <v>7.0495041522212372</v>
+        <v>7.0495041522212363</v>
       </c>
       <c r="P32">
+        <f>P31/P28</f>
+        <v>6.5441607536337356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <f>D28/P28</f>
+        <v>1.1883680029110315</v>
+      </c>
+      <c r="E35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <f>H28/P28</f>
+        <v>1.1870539955930217</v>
+      </c>
+      <c r="I35" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <f>L28/P28</f>
+        <v>1.0029312470940224</v>
+      </c>
+      <c r="M35" t="s">
+        <v>38</v>
+      </c>
+      <c r="N35" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <f>P28/P28</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <f>D29/P28</f>
+        <v>2.3951321082742032</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="H36">
+        <f>H29/P28</f>
+        <v>2.3949299533022015</v>
+      </c>
+      <c r="I36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <f>L29/P28</f>
+        <v>1.975539248387814</v>
+      </c>
+      <c r="M36" t="s">
+        <v>38</v>
+      </c>
+      <c r="N36" t="s">
+        <v>10</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
+        <f>P29/P28</f>
+        <v>1.9256069703034346</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37">
+        <f>D30/P28</f>
+        <v>4.9358157963895124</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <f>H30/P28</f>
+        <v>4.88689429316514</v>
+      </c>
+      <c r="I37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <f>L30/P28</f>
+        <v>4.0538136535468094</v>
+      </c>
+      <c r="M37" t="s">
+        <v>38</v>
+      </c>
+      <c r="N37" t="s">
+        <v>10</v>
+      </c>
+      <c r="O37">
+        <v>4</v>
+      </c>
+      <c r="P37">
+        <f>P30/P28</f>
+        <v>3.7946509794408394</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <f>D31/P28</f>
+        <v>8.5543897952170145</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <f>H31/P28</f>
+        <v>8.4167222592839668</v>
+      </c>
+      <c r="I38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38">
+        <v>8</v>
+      </c>
+      <c r="L38">
+        <f>L31/P28</f>
+        <v>7.0701679907817327</v>
+      </c>
+      <c r="M38" t="s">
+        <v>38</v>
+      </c>
+      <c r="N38" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38">
+        <v>8</v>
+      </c>
+      <c r="P38">
         <f>P31/P28</f>
         <v>6.5441607536337356</v>
       </c>
